--- a/STM32H503.xlsx
+++ b/STM32H503.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1847" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="693">
   <si>
     <t>Position</t>
   </si>
@@ -108,538 +108,538 @@
     <t>SPI3_NSS</t>
   </si>
   <si>
+    <t>RAM/ROM/PIN-O/PIN-I</t>
+  </si>
+  <si>
+    <t>RTC_OUT2</t>
+  </si>
+  <si>
+    <t>TIM2_CH1</t>
+  </si>
+  <si>
+    <t>TIM3_CH1</t>
+  </si>
+  <si>
+    <t>LPTIM2_ETR</t>
+  </si>
+  <si>
+    <t>LPTIM1_ETR</t>
+  </si>
+  <si>
+    <t>LPTIM1_IN2</t>
+  </si>
+  <si>
+    <t>SPI3_RDY</t>
+  </si>
+  <si>
+    <t>USART2_CTS/USART2_NSS</t>
+  </si>
+  <si>
+    <t>USART1_CTS/USART1_NSS</t>
+  </si>
+  <si>
+    <t>USART3_CTS/USART3_NSS</t>
+  </si>
+  <si>
+    <t>I2S3_WS/SPI3_NSS</t>
+  </si>
+  <si>
+    <t>I2S2_MCK</t>
+  </si>
+  <si>
+    <t>I2S1_SDI/SPI1_MISO</t>
+  </si>
+  <si>
+    <t>USART3_CK</t>
+  </si>
+  <si>
+    <t>TIM2_ETR</t>
+  </si>
+  <si>
+    <t>EVENTOUT</t>
+  </si>
+  <si>
+    <t>PA01</t>
+  </si>
+  <si>
+    <t>USART2_RTS</t>
+  </si>
+  <si>
+    <t>UART2-FPGA</t>
+  </si>
+  <si>
+    <t>TIM2_CH2</t>
+  </si>
+  <si>
+    <t>I2S1_WS/SPI1_NSS</t>
+  </si>
+  <si>
+    <t>LPTIM1_IN1</t>
+  </si>
+  <si>
+    <t>I2S3_CK/SPI3_SCK</t>
+  </si>
+  <si>
+    <t>USART2_DE/USART2_RTS</t>
+  </si>
+  <si>
+    <t>USART1_RX</t>
+  </si>
+  <si>
+    <t>USART2_CK</t>
+  </si>
+  <si>
+    <t>SPI2_RDY</t>
+  </si>
+  <si>
+    <t>TIM1_CH3</t>
+  </si>
+  <si>
+    <t>PA02</t>
+  </si>
+  <si>
+    <t>USART2_TX</t>
+  </si>
+  <si>
+    <t>TIM2_CH3</t>
+  </si>
+  <si>
+    <t>TIM3_ETR</t>
+  </si>
+  <si>
+    <t>LPUART1_RX</t>
+  </si>
+  <si>
+    <t>I2S1_CK/SPI1_SCK</t>
+  </si>
+  <si>
+    <t>I2S3_SDI/SPI3_MISO</t>
+  </si>
+  <si>
+    <t>USART1_TX</t>
+  </si>
+  <si>
+    <t>TIM1_CH4</t>
+  </si>
+  <si>
+    <t>PA03</t>
+  </si>
+  <si>
+    <t>SPI1_MISO</t>
+  </si>
+  <si>
+    <t>SPI1_MISO+RX</t>
+  </si>
+  <si>
+    <t>NOVA-SPI+UART</t>
+  </si>
+  <si>
+    <t>TIM2_CH4</t>
+  </si>
+  <si>
+    <t>LPUART1_TX</t>
+  </si>
+  <si>
+    <t>I2S2_WS/SPI2_NSS</t>
+  </si>
+  <si>
+    <t>I2S3_SDO/SPI3_MOSI</t>
+  </si>
+  <si>
+    <t>USART2_RX</t>
+  </si>
+  <si>
+    <t>USART1_CK</t>
+  </si>
+  <si>
+    <t>USART3_RX</t>
+  </si>
+  <si>
+    <t>TIM1_CH1N</t>
+  </si>
+  <si>
+    <t>PA04</t>
+  </si>
+  <si>
+    <t>SPI1_MOSI</t>
+  </si>
+  <si>
+    <t>SPI1_MOSI+TX</t>
+  </si>
+  <si>
+    <t>TIM1_CH2N</t>
+  </si>
+  <si>
+    <t>LPTIM2_CH1</t>
+  </si>
+  <si>
+    <t>I2S1_SDO/SPI1_MOSI</t>
+  </si>
+  <si>
+    <t>USART1_DE/USART1_RTS</t>
+  </si>
+  <si>
+    <t>USART3_TX</t>
+  </si>
+  <si>
+    <t>TIM1_BKIN</t>
+  </si>
+  <si>
+    <t>PA05</t>
+  </si>
+  <si>
+    <t>SPI1_SCK</t>
+  </si>
+  <si>
+    <t>PWR_CSTOP</t>
+  </si>
+  <si>
+    <t>LPTIM2_CH2</t>
+  </si>
+  <si>
+    <t>LPTIM1_CH1</t>
+  </si>
+  <si>
+    <t>I2S1_MCK</t>
+  </si>
+  <si>
+    <t>I2S2_CK/SPI2_SCK</t>
+  </si>
+  <si>
+    <t>LPUART1_DE/LPUART1_RTS</t>
+  </si>
+  <si>
+    <t>PA06</t>
+  </si>
+  <si>
+    <t>ADC1_INP3</t>
+  </si>
+  <si>
+    <t>PA07</t>
+  </si>
+  <si>
+    <t>USART1_RTS</t>
+  </si>
+  <si>
+    <t>PWR_CSLEEP</t>
+  </si>
+  <si>
+    <t>TIM3_CH2</t>
+  </si>
+  <si>
+    <t>AUDIOCLK</t>
+  </si>
+  <si>
+    <t>USART3_DE/USART3_RTS</t>
+  </si>
+  <si>
+    <t>I2S3_MCK</t>
+  </si>
+  <si>
+    <t>I2S2_SDI/SPI2_MISO</t>
+  </si>
+  <si>
+    <t>PA08</t>
+  </si>
+  <si>
+    <t>USB_SOF</t>
+  </si>
+  <si>
+    <t>PWM</t>
+  </si>
+  <si>
+    <t>RCC_MCO_1</t>
+  </si>
+  <si>
+    <t>TIM1_CH1</t>
+  </si>
+  <si>
+    <t>TIM3_CH3</t>
+  </si>
+  <si>
+    <t>LPTIM2_IN1</t>
+  </si>
+  <si>
+    <t>SPI1_RDY</t>
+  </si>
+  <si>
+    <t>I2S2_SDO/SPI2_MOSI</t>
+  </si>
+  <si>
+    <t>LPUART1_CTS</t>
+  </si>
+  <si>
+    <t>FDCAN1_RX</t>
+  </si>
+  <si>
+    <t>TIM1_CH4N</t>
+  </si>
+  <si>
+    <t>PA09</t>
+  </si>
+  <si>
+    <t>DEBUG_TRACED2</t>
+  </si>
+  <si>
+    <t>TIM1_CH2</t>
+  </si>
+  <si>
+    <t>PA10</t>
+  </si>
+  <si>
+    <t>LPTIM2_IN2</t>
+  </si>
+  <si>
+    <t>PA11</t>
+  </si>
+  <si>
+    <t>USB_DM</t>
+  </si>
+  <si>
+    <t>DEBUG_TRGIO</t>
+  </si>
+  <si>
+    <t>PA12</t>
+  </si>
+  <si>
+    <t>USB_DP</t>
+  </si>
+  <si>
+    <t>DEBUG_TRACED3</t>
+  </si>
+  <si>
+    <t>TIM1_ETR</t>
+  </si>
+  <si>
+    <t>TIM3_CH4</t>
+  </si>
+  <si>
+    <t>FDCAN1_TX</t>
+  </si>
+  <si>
+    <t>PA13(JTMS/SWDIO)</t>
+  </si>
+  <si>
+    <t>DEBUG_JTMS-SWDIO</t>
+  </si>
+  <si>
+    <t>COMP1_OUT</t>
+  </si>
+  <si>
+    <t>PA14(JTCK/SWCLK)</t>
+  </si>
+  <si>
+    <t>DEBUG_JTCK-SWCLK</t>
+  </si>
+  <si>
+    <t>PA15(JTDI)</t>
+  </si>
+  <si>
+    <t>USART1_CTS</t>
+  </si>
+  <si>
+    <t>DEBUG_JTDI</t>
+  </si>
+  <si>
+    <t>PB0</t>
+  </si>
+  <si>
+    <t>ADC1_INP9</t>
+  </si>
+  <si>
+    <t>SPI2-FPGA/BOOT/CTRL+ADC done</t>
+  </si>
+  <si>
+    <t>PB1</t>
+  </si>
+  <si>
+    <t>SPI2_MOSI</t>
+  </si>
+  <si>
+    <t>SPI2-FPGA</t>
+  </si>
+  <si>
+    <t>TIM1_CH3N</t>
+  </si>
+  <si>
+    <t>PB10</t>
+  </si>
+  <si>
+    <t>I2C2_SCL</t>
+  </si>
+  <si>
+    <t>PANEL-EE</t>
+  </si>
+  <si>
+    <t>I3C1_SDA</t>
+  </si>
+  <si>
+    <t>I3C2_SCL</t>
+  </si>
+  <si>
+    <t>I2C1_SDA</t>
+  </si>
+  <si>
+    <t>PB12</t>
+  </si>
+  <si>
+    <t>SPI2_NSS</t>
+  </si>
+  <si>
+    <t>SPI2-FPGA/BOOT/CTRL</t>
+  </si>
+  <si>
+    <t>I2C2_SMBA</t>
+  </si>
+  <si>
+    <t>PB13</t>
+  </si>
+  <si>
+    <t>SPI2_SCK</t>
+  </si>
+  <si>
+    <t>I2C2_SDA</t>
+  </si>
+  <si>
+    <t>I3C2_SDA</t>
+  </si>
+  <si>
+    <t>I2C1_SMBA</t>
+  </si>
+  <si>
+    <t>PB14</t>
+  </si>
+  <si>
+    <t>SPI2_MISO</t>
+  </si>
+  <si>
+    <t>PB15</t>
+  </si>
+  <si>
+    <t>RTC_REFIN</t>
+  </si>
+  <si>
+    <t>PB2</t>
+  </si>
+  <si>
+    <t>SPI3_MOSI</t>
+  </si>
+  <si>
+    <t>SPI3</t>
+  </si>
+  <si>
+    <t>LPTIM1_CH2</t>
+  </si>
+  <si>
+    <t>PB3(JTDO/TRACESWO)</t>
+  </si>
+  <si>
+    <t>DEBUG_JTDO-SWO</t>
+  </si>
+  <si>
+    <t>CRS_SYNC</t>
+  </si>
+  <si>
+    <t>PB4(NJTRST)</t>
+  </si>
+  <si>
+    <t>SPI3_MISO</t>
+  </si>
+  <si>
+    <t>DEBUG_NJTRST</t>
+  </si>
+  <si>
+    <t>PB5</t>
+  </si>
+  <si>
+    <t>SERSOR</t>
+  </si>
+  <si>
+    <t>DEBUG_TRACECLK</t>
+  </si>
+  <si>
+    <t>PB6</t>
+  </si>
+  <si>
+    <t>USART2_CTS</t>
+  </si>
+  <si>
+    <t>DEBUG_TRACED0</t>
+  </si>
+  <si>
+    <t>I3C1_SCL</t>
+  </si>
+  <si>
+    <t>I2C1_SCL</t>
+  </si>
+  <si>
+    <t>PB7</t>
+  </si>
+  <si>
+    <t>SPI3_SCK</t>
+  </si>
+  <si>
+    <t>DEBUG_TRACED1</t>
+  </si>
+  <si>
+    <t>PB8</t>
+  </si>
+  <si>
+    <t>TIM1_BKIN2</t>
+  </si>
+  <si>
+    <t>PC13</t>
+  </si>
+  <si>
+    <t>I2C RESET</t>
+  </si>
+  <si>
+    <t>PC14-OSC32_IN(OSC32_IN)</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>PC15-OSC32_OUT(OSC32_OUT)</t>
+  </si>
+  <si>
+    <t>PH0-OSC_IN(PH0)</t>
+  </si>
+  <si>
+    <t>RCC_OSC_IN</t>
+  </si>
+  <si>
+    <t>PH1-OSC_OUT(PH1)</t>
+  </si>
+  <si>
+    <t>RCC_OSC_OUT</t>
+  </si>
+  <si>
+    <t>FPGA-RESET</t>
+  </si>
+  <si>
+    <t>VBAT</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>VCAP</t>
+  </si>
+  <si>
+    <t>VDD</t>
+  </si>
+  <si>
+    <t>VDDA</t>
+  </si>
+  <si>
+    <t>VSS</t>
+  </si>
+  <si>
+    <t>VSSA</t>
+  </si>
+  <si>
     <t>SPI3-RAM/ROM/PIN-O/PIN-I</t>
-  </si>
-  <si>
-    <t>RTC_OUT2</t>
-  </si>
-  <si>
-    <t>TIM2_CH1</t>
-  </si>
-  <si>
-    <t>TIM3_CH1</t>
-  </si>
-  <si>
-    <t>LPTIM2_ETR</t>
-  </si>
-  <si>
-    <t>LPTIM1_ETR</t>
-  </si>
-  <si>
-    <t>LPTIM1_IN2</t>
-  </si>
-  <si>
-    <t>SPI3_RDY</t>
-  </si>
-  <si>
-    <t>USART2_CTS/USART2_NSS</t>
-  </si>
-  <si>
-    <t>USART1_CTS/USART1_NSS</t>
-  </si>
-  <si>
-    <t>USART3_CTS/USART3_NSS</t>
-  </si>
-  <si>
-    <t>I2S3_WS/SPI3_NSS</t>
-  </si>
-  <si>
-    <t>I2S2_MCK</t>
-  </si>
-  <si>
-    <t>I2S1_SDI/SPI1_MISO</t>
-  </si>
-  <si>
-    <t>USART3_CK</t>
-  </si>
-  <si>
-    <t>TIM2_ETR</t>
-  </si>
-  <si>
-    <t>EVENTOUT</t>
-  </si>
-  <si>
-    <t>PA01</t>
-  </si>
-  <si>
-    <t>USART2_RTS</t>
-  </si>
-  <si>
-    <t>UART2-FPGA</t>
-  </si>
-  <si>
-    <t>TIM2_CH2</t>
-  </si>
-  <si>
-    <t>I2S1_WS/SPI1_NSS</t>
-  </si>
-  <si>
-    <t>LPTIM1_IN1</t>
-  </si>
-  <si>
-    <t>I2S3_CK/SPI3_SCK</t>
-  </si>
-  <si>
-    <t>USART2_DE/USART2_RTS</t>
-  </si>
-  <si>
-    <t>USART1_RX</t>
-  </si>
-  <si>
-    <t>USART2_CK</t>
-  </si>
-  <si>
-    <t>SPI2_RDY</t>
-  </si>
-  <si>
-    <t>TIM1_CH3</t>
-  </si>
-  <si>
-    <t>PA02</t>
-  </si>
-  <si>
-    <t>USART2_TX</t>
-  </si>
-  <si>
-    <t>TIM2_CH3</t>
-  </si>
-  <si>
-    <t>TIM3_ETR</t>
-  </si>
-  <si>
-    <t>LPUART1_RX</t>
-  </si>
-  <si>
-    <t>I2S1_CK/SPI1_SCK</t>
-  </si>
-  <si>
-    <t>I2S3_SDI/SPI3_MISO</t>
-  </si>
-  <si>
-    <t>USART1_TX</t>
-  </si>
-  <si>
-    <t>TIM1_CH4</t>
-  </si>
-  <si>
-    <t>PA03</t>
-  </si>
-  <si>
-    <t>SPI1_MISO</t>
-  </si>
-  <si>
-    <t>SPI1_MISO+RX</t>
-  </si>
-  <si>
-    <t>NOVA-SPI+UART</t>
-  </si>
-  <si>
-    <t>TIM2_CH4</t>
-  </si>
-  <si>
-    <t>LPUART1_TX</t>
-  </si>
-  <si>
-    <t>I2S2_WS/SPI2_NSS</t>
-  </si>
-  <si>
-    <t>I2S3_SDO/SPI3_MOSI</t>
-  </si>
-  <si>
-    <t>USART2_RX</t>
-  </si>
-  <si>
-    <t>USART1_CK</t>
-  </si>
-  <si>
-    <t>USART3_RX</t>
-  </si>
-  <si>
-    <t>TIM1_CH1N</t>
-  </si>
-  <si>
-    <t>PA04</t>
-  </si>
-  <si>
-    <t>SPI1_MOSI</t>
-  </si>
-  <si>
-    <t>SPI1_MOSI+TX</t>
-  </si>
-  <si>
-    <t>TIM1_CH2N</t>
-  </si>
-  <si>
-    <t>LPTIM2_CH1</t>
-  </si>
-  <si>
-    <t>I2S1_SDO/SPI1_MOSI</t>
-  </si>
-  <si>
-    <t>USART1_DE/USART1_RTS</t>
-  </si>
-  <si>
-    <t>USART3_TX</t>
-  </si>
-  <si>
-    <t>TIM1_BKIN</t>
-  </si>
-  <si>
-    <t>PA05</t>
-  </si>
-  <si>
-    <t>SPI1_SCK</t>
-  </si>
-  <si>
-    <t>PWR_CSTOP</t>
-  </si>
-  <si>
-    <t>LPTIM2_CH2</t>
-  </si>
-  <si>
-    <t>LPTIM1_CH1</t>
-  </si>
-  <si>
-    <t>I2S1_MCK</t>
-  </si>
-  <si>
-    <t>I2S2_CK/SPI2_SCK</t>
-  </si>
-  <si>
-    <t>LPUART1_DE/LPUART1_RTS</t>
-  </si>
-  <si>
-    <t>PA06</t>
-  </si>
-  <si>
-    <t>ADC1_INP3</t>
-  </si>
-  <si>
-    <t>PA07</t>
-  </si>
-  <si>
-    <t>USART1_RTS</t>
-  </si>
-  <si>
-    <t>PWR_CSLEEP</t>
-  </si>
-  <si>
-    <t>TIM3_CH2</t>
-  </si>
-  <si>
-    <t>AUDIOCLK</t>
-  </si>
-  <si>
-    <t>USART3_DE/USART3_RTS</t>
-  </si>
-  <si>
-    <t>I2S3_MCK</t>
-  </si>
-  <si>
-    <t>I2S2_SDI/SPI2_MISO</t>
-  </si>
-  <si>
-    <t>PA08</t>
-  </si>
-  <si>
-    <t>USB_SOF</t>
-  </si>
-  <si>
-    <t>PWM</t>
-  </si>
-  <si>
-    <t>RCC_MCO_1</t>
-  </si>
-  <si>
-    <t>TIM1_CH1</t>
-  </si>
-  <si>
-    <t>TIM3_CH3</t>
-  </si>
-  <si>
-    <t>LPTIM2_IN1</t>
-  </si>
-  <si>
-    <t>SPI1_RDY</t>
-  </si>
-  <si>
-    <t>I2S2_SDO/SPI2_MOSI</t>
-  </si>
-  <si>
-    <t>LPUART1_CTS</t>
-  </si>
-  <si>
-    <t>FDCAN1_RX</t>
-  </si>
-  <si>
-    <t>TIM1_CH4N</t>
-  </si>
-  <si>
-    <t>PA09</t>
-  </si>
-  <si>
-    <t>DEBUG_TRACED2</t>
-  </si>
-  <si>
-    <t>TIM1_CH2</t>
-  </si>
-  <si>
-    <t>PA10</t>
-  </si>
-  <si>
-    <t>LPTIM2_IN2</t>
-  </si>
-  <si>
-    <t>PA11</t>
-  </si>
-  <si>
-    <t>USB_DM</t>
-  </si>
-  <si>
-    <t>DEBUG_TRGIO</t>
-  </si>
-  <si>
-    <t>PA12</t>
-  </si>
-  <si>
-    <t>USB_DP</t>
-  </si>
-  <si>
-    <t>DEBUG_TRACED3</t>
-  </si>
-  <si>
-    <t>TIM1_ETR</t>
-  </si>
-  <si>
-    <t>TIM3_CH4</t>
-  </si>
-  <si>
-    <t>FDCAN1_TX</t>
-  </si>
-  <si>
-    <t>PA13(JTMS/SWDIO)</t>
-  </si>
-  <si>
-    <t>DEBUG_JTMS-SWDIO</t>
-  </si>
-  <si>
-    <t>COMP1_OUT</t>
-  </si>
-  <si>
-    <t>PA14(JTCK/SWCLK)</t>
-  </si>
-  <si>
-    <t>DEBUG_JTCK-SWCLK</t>
-  </si>
-  <si>
-    <t>PA15(JTDI)</t>
-  </si>
-  <si>
-    <t>USART1_CTS</t>
-  </si>
-  <si>
-    <t>DEBUG_JTDI</t>
-  </si>
-  <si>
-    <t>PB0</t>
-  </si>
-  <si>
-    <t>ADC1_INP9</t>
-  </si>
-  <si>
-    <t>SPI2-FPGA/BOOT/CTRL+ADC done</t>
-  </si>
-  <si>
-    <t>PB1</t>
-  </si>
-  <si>
-    <t>SPI2_MOSI</t>
-  </si>
-  <si>
-    <t>SPI2-FPGA</t>
-  </si>
-  <si>
-    <t>TIM1_CH3N</t>
-  </si>
-  <si>
-    <t>PB10</t>
-  </si>
-  <si>
-    <t>I2C2_SCL</t>
-  </si>
-  <si>
-    <t>PANEL-EE</t>
-  </si>
-  <si>
-    <t>I3C1_SDA</t>
-  </si>
-  <si>
-    <t>I3C2_SCL</t>
-  </si>
-  <si>
-    <t>I2C1_SDA</t>
-  </si>
-  <si>
-    <t>PB12</t>
-  </si>
-  <si>
-    <t>SPI2_NSS</t>
-  </si>
-  <si>
-    <t>SPI2-FPGA/BOOT/CTRL</t>
-  </si>
-  <si>
-    <t>I2C2_SMBA</t>
-  </si>
-  <si>
-    <t>PB13</t>
-  </si>
-  <si>
-    <t>SPI2_SCK</t>
-  </si>
-  <si>
-    <t>I2C2_SDA</t>
-  </si>
-  <si>
-    <t>I3C2_SDA</t>
-  </si>
-  <si>
-    <t>I2C1_SMBA</t>
-  </si>
-  <si>
-    <t>PB14</t>
-  </si>
-  <si>
-    <t>SPI2_MISO</t>
-  </si>
-  <si>
-    <t>PB15</t>
-  </si>
-  <si>
-    <t>RTC_REFIN</t>
-  </si>
-  <si>
-    <t>PB2</t>
-  </si>
-  <si>
-    <t>SPI3_MOSI</t>
-  </si>
-  <si>
-    <t>SPI3</t>
-  </si>
-  <si>
-    <t>LPTIM1_CH2</t>
-  </si>
-  <si>
-    <t>PB3(JTDO/TRACESWO)</t>
-  </si>
-  <si>
-    <t>DEBUG_JTDO-SWO</t>
-  </si>
-  <si>
-    <t>CRS_SYNC</t>
-  </si>
-  <si>
-    <t>PB4(NJTRST)</t>
-  </si>
-  <si>
-    <t>SPI3_MISO</t>
-  </si>
-  <si>
-    <t>DEBUG_NJTRST</t>
-  </si>
-  <si>
-    <t>PB5</t>
-  </si>
-  <si>
-    <t>SERSOR</t>
-  </si>
-  <si>
-    <t>DEBUG_TRACECLK</t>
-  </si>
-  <si>
-    <t>PB6</t>
-  </si>
-  <si>
-    <t>USART2_CTS</t>
-  </si>
-  <si>
-    <t>DEBUG_TRACED0</t>
-  </si>
-  <si>
-    <t>I3C1_SCL</t>
-  </si>
-  <si>
-    <t>I2C1_SCL</t>
-  </si>
-  <si>
-    <t>PB7</t>
-  </si>
-  <si>
-    <t>SPI3_SCK</t>
-  </si>
-  <si>
-    <t>DEBUG_TRACED1</t>
-  </si>
-  <si>
-    <t>PB8</t>
-  </si>
-  <si>
-    <t>TIM1_BKIN2</t>
-  </si>
-  <si>
-    <t>PC13</t>
-  </si>
-  <si>
-    <t>I2C RESET</t>
-  </si>
-  <si>
-    <t>PC14-OSC32_IN(OSC32_IN)</t>
-  </si>
-  <si>
-    <t>LED</t>
-  </si>
-  <si>
-    <t>PC15-OSC32_OUT(OSC32_OUT)</t>
-  </si>
-  <si>
-    <t>SPI1-CS-TXE8124</t>
-  </si>
-  <si>
-    <t>PH0-OSC_IN(PH0)</t>
-  </si>
-  <si>
-    <t>RCC_OSC_IN</t>
-  </si>
-  <si>
-    <t>PH1-OSC_OUT(PH1)</t>
-  </si>
-  <si>
-    <t>RCC_OSC_OUT</t>
-  </si>
-  <si>
-    <t>FPGA-RESET</t>
-  </si>
-  <si>
-    <t>VBAT</t>
-  </si>
-  <si>
-    <t>Power</t>
-  </si>
-  <si>
-    <t>VCAP</t>
-  </si>
-  <si>
-    <t>VDD</t>
-  </si>
-  <si>
-    <t>VDDA</t>
-  </si>
-  <si>
-    <t>VSS</t>
-  </si>
-  <si>
-    <t>VSSA</t>
   </si>
   <si>
     <t>MCU-I/O-HW-AUTOID</t>
@@ -2134,7 +2134,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2155,8 +2155,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FFFF"/>
-        <bgColor rgb="FF00FFFF"/>
+        <fgColor rgb="FFD0E0E3"/>
+        <bgColor rgb="FFD0E0E3"/>
       </patternFill>
     </fill>
     <fill>
@@ -2169,6 +2169,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF4A86E8"/>
         <bgColor rgb="FF4A86E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FFFF"/>
+        <bgColor rgb="FF00FFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -2190,7 +2196,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2230,6 +2236,9 @@
     <xf borderId="0" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -2243,7 +2252,7 @@
     <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="9" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -3607,7 +3616,7 @@
       <c r="D20" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="12" t="s">
         <v>143</v>
       </c>
       <c r="H20" s="5" t="s">
@@ -3742,7 +3751,7 @@
       <c r="D23" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="12" t="s">
         <v>156</v>
       </c>
       <c r="H23" s="5" t="s">
@@ -4127,7 +4136,7 @@
       <c r="N30" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="O30" s="12" t="s">
+      <c r="O30" s="13" t="s">
         <v>149</v>
       </c>
       <c r="P30" s="5" t="s">
@@ -4310,7 +4319,7 @@
       <c r="N33" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="O33" s="12" t="s">
+      <c r="O33" s="13" t="s">
         <v>160</v>
       </c>
       <c r="P33" s="5" t="s">
@@ -4379,9 +4388,7 @@
       <c r="C36" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E36" s="10" t="s">
-        <v>195</v>
-      </c>
+      <c r="E36" s="5"/>
       <c r="V36" s="5" t="s">
         <v>46</v>
       </c>
@@ -4391,13 +4398,13 @@
         <v>5.0</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="V37" s="5" t="s">
         <v>46</v>
@@ -4408,16 +4415,16 @@
         <v>6.0</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D38" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="F38" s="5"/>
       <c r="V38" s="5" t="s">
@@ -4429,10 +4436,10 @@
         <v>1.0</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="40" ht="22.5" customHeight="1">
@@ -4440,10 +4447,10 @@
         <v>22.0</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" ht="22.5" customHeight="1">
@@ -4451,10 +4458,10 @@
         <v>46.0</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
@@ -4462,10 +4469,10 @@
         <v>24.0</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
@@ -4473,10 +4480,10 @@
         <v>36.0</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44" ht="22.5" customHeight="1">
@@ -4484,10 +4491,10 @@
         <v>48.0</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
@@ -4495,10 +4502,10 @@
         <v>9.0</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
@@ -4506,10 +4513,10 @@
         <v>23.0</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47" ht="22.5" customHeight="1">
@@ -4517,10 +4524,10 @@
         <v>35.0</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
@@ -4528,10 +4535,10 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
@@ -4539,10 +4546,10 @@
         <v>8.0</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -4692,8 +4699,8 @@
       <c r="D4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>30</v>
+      <c r="E4" s="12" t="s">
+        <v>207</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
@@ -5020,8 +5027,8 @@
       <c r="D10" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>30</v>
+      <c r="E10" s="12" t="s">
+        <v>207</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>88</v>
@@ -5049,8 +5056,8 @@
       <c r="D11" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>30</v>
+      <c r="E11" s="12" t="s">
+        <v>207</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>209</v>
@@ -5469,8 +5476,8 @@
       <c r="D19" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>30</v>
+      <c r="E19" s="12" t="s">
+        <v>207</v>
       </c>
       <c r="F19" s="11" t="s">
         <v>209</v>
@@ -5534,7 +5541,7 @@
       <c r="D20" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="12" t="s">
         <v>143</v>
       </c>
       <c r="H20" s="5" t="s">
@@ -5672,7 +5679,7 @@
       <c r="D23" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="12" t="s">
         <v>156</v>
       </c>
       <c r="H23" s="5" t="s">
@@ -6064,7 +6071,7 @@
       <c r="N30" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="O30" s="12" t="s">
+      <c r="O30" s="13" t="s">
         <v>149</v>
       </c>
       <c r="P30" s="5" t="s">
@@ -6254,7 +6261,7 @@
       <c r="N33" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="O33" s="12" t="s">
+      <c r="O33" s="13" t="s">
         <v>160</v>
       </c>
       <c r="P33" s="5" t="s">
@@ -6335,13 +6342,13 @@
         <v>5.0</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="V37" s="5" t="s">
         <v>46</v>
@@ -6352,16 +6359,16 @@
         <v>6.0</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D38" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>200</v>
       </c>
       <c r="F38" s="5"/>
       <c r="V38" s="5" t="s">
@@ -6373,10 +6380,10 @@
         <v>1.0</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="40" ht="22.5" customHeight="1">
@@ -6384,10 +6391,10 @@
         <v>22.0</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" ht="22.5" customHeight="1">
@@ -6395,10 +6402,10 @@
         <v>46.0</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
@@ -6406,10 +6413,10 @@
         <v>24.0</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
@@ -6417,10 +6424,10 @@
         <v>36.0</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44" ht="22.5" customHeight="1">
@@ -6428,10 +6435,10 @@
         <v>48.0</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
@@ -6439,10 +6446,10 @@
         <v>9.0</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
@@ -6450,10 +6457,10 @@
         <v>23.0</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47" ht="22.5" customHeight="1">
@@ -6461,10 +6468,10 @@
         <v>35.0</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
@@ -6472,10 +6479,10 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
@@ -6483,10 +6490,10 @@
         <v>8.0</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -6519,224 +6526,224 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="14" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="14" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="14" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="F6" s="14"/>
+      <c r="F6" s="15"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="F7" s="14"/>
+      <c r="F7" s="15"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="F8" s="14"/>
+      <c r="F8" s="15"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="F9" s="14"/>
+      <c r="F9" s="15"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F10" s="14"/>
+      <c r="F10" s="15"/>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="14"/>
+      <c r="F11" s="15"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="14"/>
+      <c r="F12" s="15"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="F13" s="14"/>
+      <c r="F13" s="15"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="F14" s="14"/>
+      <c r="F14" s="15"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="F15" s="14"/>
+      <c r="F15" s="15"/>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="14" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="14" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="14" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="14" t="s">
         <v>241</v>
       </c>
     </row>
@@ -6763,27 +6770,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13"/>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13">
+      <c r="A1" s="14"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14">
         <v>14.5</v>
       </c>
-      <c r="H1" s="13">
+      <c r="H1" s="14">
         <v>38.0</v>
       </c>
-      <c r="I1" s="13">
+      <c r="I1" s="14">
         <v>24.0</v>
       </c>
-      <c r="J1" s="15">
+      <c r="J1" s="16">
         <v>28.0</v>
       </c>
-      <c r="K1" s="13">
+      <c r="K1" s="14">
         <v>22.0</v>
       </c>
-      <c r="L1" s="16">
+      <c r="L1" s="17">
         <f>G1+H1+I1+K1</f>
         <v>98.5</v>
       </c>
@@ -6801,22 +6808,22 @@
       <c r="D2" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="14" t="s">
         <v>251</v>
       </c>
     </row>
@@ -6830,7 +6837,7 @@
       <c r="C3" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -6844,7 +6851,7 @@
       <c r="C4" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="D4" s="19"/>
+      <c r="D4" s="20"/>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="6" t="s">
@@ -6856,7 +6863,7 @@
       <c r="C5" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -6870,7 +6877,7 @@
       <c r="C6" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -6884,7 +6891,7 @@
       <c r="C7" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -6898,7 +6905,7 @@
       <c r="C8" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -6912,7 +6919,7 @@
       <c r="C9" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -6926,7 +6933,7 @@
       <c r="C10" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -6940,7 +6947,7 @@
       <c r="C11" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -6954,7 +6961,7 @@
       <c r="C12" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -6968,7 +6975,7 @@
       <c r="C13" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -6982,7 +6989,7 @@
       <c r="C14" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -6996,7 +7003,7 @@
       <c r="C15" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -7010,7 +7017,7 @@
       <c r="C16" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -7024,7 +7031,7 @@
       <c r="C17" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -7038,7 +7045,7 @@
       <c r="C18" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -7052,7 +7059,7 @@
       <c r="C19" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -7069,7 +7076,7 @@
       <c r="D20" s="4">
         <v>18.0</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="14">
         <v>1.0</v>
       </c>
     </row>
@@ -7086,7 +7093,7 @@
       <c r="D21" s="4">
         <v>18.0</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="17">
         <f t="shared" ref="F21:F83" si="1">F20+1</f>
         <v>2</v>
       </c>
@@ -7104,7 +7111,7 @@
       <c r="D22" s="4">
         <v>18.0</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="17">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
@@ -7122,7 +7129,7 @@
       <c r="D23" s="4">
         <v>18.0</v>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="17">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -7140,7 +7147,7 @@
       <c r="D24" s="4">
         <v>18.0</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="17">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
@@ -7158,7 +7165,7 @@
       <c r="D25" s="4">
         <v>18.0</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="17">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
@@ -7176,7 +7183,7 @@
       <c r="D26" s="4">
         <v>18.0</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="17">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -7194,7 +7201,7 @@
       <c r="D27" s="4">
         <v>18.0</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="17">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
@@ -7212,7 +7219,7 @@
       <c r="D28" s="4">
         <v>18.0</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="17">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -7230,7 +7237,7 @@
       <c r="D29" s="4">
         <v>18.0</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="17">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -7248,7 +7255,7 @@
       <c r="D30" s="4">
         <v>18.0</v>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="17">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
@@ -7266,7 +7273,7 @@
       <c r="D31" s="4">
         <v>18.0</v>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="17">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -7284,7 +7291,7 @@
       <c r="D32" s="4">
         <v>18.0</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="17">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
@@ -7302,7 +7309,7 @@
       <c r="D33" s="4">
         <v>18.0</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="17">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
@@ -7320,7 +7327,7 @@
       <c r="D34" s="4">
         <v>18.0</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="17">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
@@ -7338,7 +7345,7 @@
       <c r="D35" s="4">
         <v>18.0</v>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="17">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
@@ -7356,7 +7363,7 @@
       <c r="D36" s="4">
         <v>18.0</v>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="17">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
@@ -7374,7 +7381,7 @@
       <c r="D37" s="4">
         <v>18.0</v>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="17">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
@@ -7392,7 +7399,7 @@
       <c r="D38" s="4">
         <v>18.0</v>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="17">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
@@ -7410,7 +7417,7 @@
       <c r="D39" s="4">
         <v>18.0</v>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="17">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
@@ -7428,7 +7435,7 @@
       <c r="D40" s="4">
         <v>18.0</v>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="17">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
@@ -7446,7 +7453,7 @@
       <c r="D41" s="4">
         <v>18.0</v>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="17">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
@@ -7464,7 +7471,7 @@
       <c r="D42" s="4">
         <v>18.0</v>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="17">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
@@ -7482,7 +7489,7 @@
       <c r="D43" s="4">
         <v>18.0</v>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="17">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
@@ -7500,7 +7507,7 @@
       <c r="D44" s="4">
         <v>18.0</v>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="17">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
@@ -7518,7 +7525,7 @@
       <c r="D45" s="4">
         <v>18.0</v>
       </c>
-      <c r="F45" s="16">
+      <c r="F45" s="17">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
@@ -7536,7 +7543,7 @@
       <c r="D46" s="4">
         <v>18.0</v>
       </c>
-      <c r="F46" s="16">
+      <c r="F46" s="17">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
@@ -7554,7 +7561,7 @@
       <c r="D47" s="4">
         <v>18.0</v>
       </c>
-      <c r="F47" s="16">
+      <c r="F47" s="17">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
@@ -7572,7 +7579,7 @@
       <c r="D48" s="4">
         <v>18.0</v>
       </c>
-      <c r="F48" s="16">
+      <c r="F48" s="17">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
@@ -7590,7 +7597,7 @@
       <c r="D49" s="4">
         <v>18.0</v>
       </c>
-      <c r="F49" s="16">
+      <c r="F49" s="17">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
@@ -7608,7 +7615,7 @@
       <c r="D50" s="4">
         <v>18.0</v>
       </c>
-      <c r="F50" s="16">
+      <c r="F50" s="17">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
@@ -7626,7 +7633,7 @@
       <c r="D51" s="4">
         <v>18.0</v>
       </c>
-      <c r="F51" s="16">
+      <c r="F51" s="17">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
@@ -7644,7 +7651,7 @@
       <c r="D52" s="4">
         <v>18.0</v>
       </c>
-      <c r="F52" s="16">
+      <c r="F52" s="17">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
@@ -7662,7 +7669,7 @@
       <c r="D53" s="4">
         <v>18.0</v>
       </c>
-      <c r="F53" s="16">
+      <c r="F53" s="17">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
@@ -7680,7 +7687,7 @@
       <c r="D54" s="4">
         <v>18.0</v>
       </c>
-      <c r="F54" s="16">
+      <c r="F54" s="17">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
@@ -7698,7 +7705,7 @@
       <c r="D55" s="4">
         <v>18.0</v>
       </c>
-      <c r="F55" s="16">
+      <c r="F55" s="17">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
@@ -7716,7 +7723,7 @@
       <c r="D56" s="4">
         <v>18.0</v>
       </c>
-      <c r="F56" s="16">
+      <c r="F56" s="17">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
@@ -7734,7 +7741,7 @@
       <c r="D57" s="4">
         <v>18.0</v>
       </c>
-      <c r="F57" s="16">
+      <c r="F57" s="17">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
@@ -7752,7 +7759,7 @@
       <c r="D58" s="4">
         <v>18.0</v>
       </c>
-      <c r="F58" s="16">
+      <c r="F58" s="17">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
@@ -7770,7 +7777,7 @@
       <c r="D59" s="4">
         <v>18.0</v>
       </c>
-      <c r="F59" s="16">
+      <c r="F59" s="17">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
@@ -7788,7 +7795,7 @@
       <c r="D60" s="4">
         <v>18.0</v>
       </c>
-      <c r="F60" s="16">
+      <c r="F60" s="17">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
@@ -7806,7 +7813,7 @@
       <c r="D61" s="4">
         <v>18.0</v>
       </c>
-      <c r="F61" s="16">
+      <c r="F61" s="17">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
@@ -7824,7 +7831,7 @@
       <c r="D62" s="4">
         <v>18.0</v>
       </c>
-      <c r="F62" s="16">
+      <c r="F62" s="17">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
@@ -7842,7 +7849,7 @@
       <c r="D63" s="4">
         <v>18.0</v>
       </c>
-      <c r="F63" s="16">
+      <c r="F63" s="17">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
@@ -7860,7 +7867,7 @@
       <c r="D64" s="4">
         <v>18.0</v>
       </c>
-      <c r="F64" s="16">
+      <c r="F64" s="17">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
@@ -7878,7 +7885,7 @@
       <c r="D65" s="4">
         <v>18.0</v>
       </c>
-      <c r="F65" s="16">
+      <c r="F65" s="17">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
@@ -7896,7 +7903,7 @@
       <c r="D66" s="4">
         <v>18.0</v>
       </c>
-      <c r="F66" s="16">
+      <c r="F66" s="17">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
@@ -7914,7 +7921,7 @@
       <c r="D67" s="4">
         <v>18.0</v>
       </c>
-      <c r="F67" s="16">
+      <c r="F67" s="17">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
@@ -7932,7 +7939,7 @@
       <c r="D68" s="4">
         <v>18.0</v>
       </c>
-      <c r="F68" s="16">
+      <c r="F68" s="17">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
@@ -7950,7 +7957,7 @@
       <c r="D69" s="4">
         <v>18.0</v>
       </c>
-      <c r="F69" s="16">
+      <c r="F69" s="17">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
@@ -7968,7 +7975,7 @@
       <c r="D70" s="4">
         <v>18.0</v>
       </c>
-      <c r="F70" s="16">
+      <c r="F70" s="17">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
@@ -7986,7 +7993,7 @@
       <c r="D71" s="4">
         <v>18.0</v>
       </c>
-      <c r="F71" s="16">
+      <c r="F71" s="17">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
@@ -8004,7 +8011,7 @@
       <c r="D72" s="4">
         <v>18.0</v>
       </c>
-      <c r="F72" s="16">
+      <c r="F72" s="17">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
@@ -8022,7 +8029,7 @@
       <c r="D73" s="4">
         <v>18.0</v>
       </c>
-      <c r="F73" s="16">
+      <c r="F73" s="17">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
@@ -8040,7 +8047,7 @@
       <c r="D74" s="4">
         <v>18.0</v>
       </c>
-      <c r="F74" s="16">
+      <c r="F74" s="17">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
@@ -8058,7 +8065,7 @@
       <c r="D75" s="4">
         <v>18.0</v>
       </c>
-      <c r="F75" s="16">
+      <c r="F75" s="17">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
@@ -8076,7 +8083,7 @@
       <c r="D76" s="4">
         <v>18.0</v>
       </c>
-      <c r="F76" s="16">
+      <c r="F76" s="17">
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
@@ -8094,7 +8101,7 @@
       <c r="D77" s="4">
         <v>18.0</v>
       </c>
-      <c r="F77" s="16">
+      <c r="F77" s="17">
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
@@ -8112,7 +8119,7 @@
       <c r="D78" s="4">
         <v>18.0</v>
       </c>
-      <c r="F78" s="16">
+      <c r="F78" s="17">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
@@ -8130,7 +8137,7 @@
       <c r="D79" s="4">
         <v>18.0</v>
       </c>
-      <c r="F79" s="16">
+      <c r="F79" s="17">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
@@ -8148,7 +8155,7 @@
       <c r="D80" s="4">
         <v>18.0</v>
       </c>
-      <c r="F80" s="16">
+      <c r="F80" s="17">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
@@ -8166,7 +8173,7 @@
       <c r="D81" s="4">
         <v>18.0</v>
       </c>
-      <c r="F81" s="16">
+      <c r="F81" s="17">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
@@ -8184,7 +8191,7 @@
       <c r="D82" s="4">
         <v>18.0</v>
       </c>
-      <c r="F82" s="16">
+      <c r="F82" s="17">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
@@ -8202,7 +8209,7 @@
       <c r="D83" s="4">
         <v>18.0</v>
       </c>
-      <c r="F83" s="16">
+      <c r="F83" s="17">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
@@ -8220,14 +8227,14 @@
       <c r="D84" s="4">
         <v>33.0</v>
       </c>
-      <c r="E84" s="13"/>
-      <c r="G84" s="13">
+      <c r="E84" s="14"/>
+      <c r="G84" s="14">
         <v>1.0</v>
       </c>
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
-      <c r="J84" s="13"/>
-      <c r="K84" s="13"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+      <c r="K84" s="14"/>
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="6" t="s">
@@ -8242,7 +8249,7 @@
       <c r="D85" s="4">
         <v>33.0</v>
       </c>
-      <c r="G85" s="16">
+      <c r="G85" s="17">
         <f t="shared" ref="G85:G98" si="2">G84+1</f>
         <v>2</v>
       </c>
@@ -8260,8 +8267,8 @@
       <c r="D86" s="4">
         <v>33.0</v>
       </c>
-      <c r="E86" s="13"/>
-      <c r="G86" s="16">
+      <c r="E86" s="14"/>
+      <c r="G86" s="17">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
@@ -8279,7 +8286,7 @@
       <c r="D87" s="4">
         <v>33.0</v>
       </c>
-      <c r="G87" s="16">
+      <c r="G87" s="17">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
@@ -8297,7 +8304,7 @@
       <c r="D88" s="4">
         <v>33.0</v>
       </c>
-      <c r="G88" s="16">
+      <c r="G88" s="17">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
@@ -8309,13 +8316,13 @@
       <c r="B89" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="C89" s="20" t="s">
+      <c r="C89" s="21" t="s">
         <v>428</v>
       </c>
       <c r="D89" s="4">
         <v>33.0</v>
       </c>
-      <c r="G89" s="16">
+      <c r="G89" s="17">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
@@ -8333,7 +8340,7 @@
       <c r="D90" s="4">
         <v>33.0</v>
       </c>
-      <c r="G90" s="16">
+      <c r="G90" s="17">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
@@ -8351,7 +8358,7 @@
       <c r="D91" s="4">
         <v>33.0</v>
       </c>
-      <c r="G91" s="16">
+      <c r="G91" s="17">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
@@ -8369,7 +8376,7 @@
       <c r="D92" s="4">
         <v>33.0</v>
       </c>
-      <c r="G92" s="16">
+      <c r="G92" s="17">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
@@ -8387,7 +8394,7 @@
       <c r="D93" s="4">
         <v>33.0</v>
       </c>
-      <c r="G93" s="16">
+      <c r="G93" s="17">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
@@ -8405,7 +8412,7 @@
       <c r="D94" s="4">
         <v>33.0</v>
       </c>
-      <c r="G94" s="16">
+      <c r="G94" s="17">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
@@ -8423,7 +8430,7 @@
       <c r="D95" s="4">
         <v>33.0</v>
       </c>
-      <c r="G95" s="16">
+      <c r="G95" s="17">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
@@ -8441,7 +8448,7 @@
       <c r="D96" s="4">
         <v>33.0</v>
       </c>
-      <c r="G96" s="16">
+      <c r="G96" s="17">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
@@ -8459,7 +8466,7 @@
       <c r="D97" s="4">
         <v>33.0</v>
       </c>
-      <c r="G97" s="16">
+      <c r="G97" s="17">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
@@ -8477,7 +8484,7 @@
       <c r="D98" s="4">
         <v>33.0</v>
       </c>
-      <c r="G98" s="16">
+      <c r="G98" s="17">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
@@ -8495,7 +8502,7 @@
       <c r="D99" s="4">
         <v>33.0</v>
       </c>
-      <c r="H99" s="13">
+      <c r="H99" s="14">
         <v>1.0</v>
       </c>
     </row>
@@ -8512,7 +8519,7 @@
       <c r="D100" s="4">
         <v>33.0</v>
       </c>
-      <c r="H100" s="16">
+      <c r="H100" s="17">
         <f t="shared" ref="H100:H136" si="3">H99+1</f>
         <v>2</v>
       </c>
@@ -8530,7 +8537,7 @@
       <c r="D101" s="4">
         <v>33.0</v>
       </c>
-      <c r="H101" s="16">
+      <c r="H101" s="17">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
@@ -8548,7 +8555,7 @@
       <c r="D102" s="4">
         <v>33.0</v>
       </c>
-      <c r="H102" s="16">
+      <c r="H102" s="17">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
@@ -8566,7 +8573,7 @@
       <c r="D103" s="4">
         <v>33.0</v>
       </c>
-      <c r="H103" s="16">
+      <c r="H103" s="17">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
@@ -8584,7 +8591,7 @@
       <c r="D104" s="4">
         <v>33.0</v>
       </c>
-      <c r="H104" s="16">
+      <c r="H104" s="17">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
@@ -8602,7 +8609,7 @@
       <c r="D105" s="4">
         <v>33.0</v>
       </c>
-      <c r="H105" s="16">
+      <c r="H105" s="17">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -8620,7 +8627,7 @@
       <c r="D106" s="4">
         <v>33.0</v>
       </c>
-      <c r="H106" s="16">
+      <c r="H106" s="17">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
@@ -8638,7 +8645,7 @@
       <c r="D107" s="4">
         <v>33.0</v>
       </c>
-      <c r="H107" s="16">
+      <c r="H107" s="17">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
@@ -8656,7 +8663,7 @@
       <c r="D108" s="4">
         <v>33.0</v>
       </c>
-      <c r="H108" s="16">
+      <c r="H108" s="17">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -8674,7 +8681,7 @@
       <c r="D109" s="4">
         <v>33.0</v>
       </c>
-      <c r="H109" s="16">
+      <c r="H109" s="17">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
@@ -8692,7 +8699,7 @@
       <c r="D110" s="4">
         <v>33.0</v>
       </c>
-      <c r="H110" s="16">
+      <c r="H110" s="17">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
@@ -8710,7 +8717,7 @@
       <c r="D111" s="4">
         <v>33.0</v>
       </c>
-      <c r="H111" s="16">
+      <c r="H111" s="17">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
@@ -8728,7 +8735,7 @@
       <c r="D112" s="4">
         <v>33.0</v>
       </c>
-      <c r="H112" s="16">
+      <c r="H112" s="17">
         <f t="shared" si="3"/>
         <v>14</v>
       </c>
@@ -8746,7 +8753,7 @@
       <c r="D113" s="4">
         <v>33.0</v>
       </c>
-      <c r="H113" s="16">
+      <c r="H113" s="17">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
@@ -8764,7 +8771,7 @@
       <c r="D114" s="4">
         <v>33.0</v>
       </c>
-      <c r="H114" s="16">
+      <c r="H114" s="17">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -8782,7 +8789,7 @@
       <c r="D115" s="4">
         <v>33.0</v>
       </c>
-      <c r="H115" s="16">
+      <c r="H115" s="17">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
@@ -8800,7 +8807,7 @@
       <c r="D116" s="4">
         <v>33.0</v>
       </c>
-      <c r="H116" s="16">
+      <c r="H116" s="17">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
@@ -8818,7 +8825,7 @@
       <c r="D117" s="4">
         <v>33.0</v>
       </c>
-      <c r="H117" s="16">
+      <c r="H117" s="17">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
@@ -8836,7 +8843,7 @@
       <c r="D118" s="4">
         <v>33.0</v>
       </c>
-      <c r="H118" s="16">
+      <c r="H118" s="17">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
@@ -8854,7 +8861,7 @@
       <c r="D119" s="4">
         <v>33.0</v>
       </c>
-      <c r="H119" s="16">
+      <c r="H119" s="17">
         <f t="shared" si="3"/>
         <v>21</v>
       </c>
@@ -8872,7 +8879,7 @@
       <c r="D120" s="4">
         <v>33.0</v>
       </c>
-      <c r="H120" s="16">
+      <c r="H120" s="17">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -8890,7 +8897,7 @@
       <c r="D121" s="4">
         <v>33.0</v>
       </c>
-      <c r="H121" s="16">
+      <c r="H121" s="17">
         <f t="shared" si="3"/>
         <v>23</v>
       </c>
@@ -8908,7 +8915,7 @@
       <c r="D122" s="4">
         <v>33.0</v>
       </c>
-      <c r="H122" s="16">
+      <c r="H122" s="17">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
@@ -8926,7 +8933,7 @@
       <c r="D123" s="4">
         <v>33.0</v>
       </c>
-      <c r="H123" s="16">
+      <c r="H123" s="17">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
@@ -8944,7 +8951,7 @@
       <c r="D124" s="4">
         <v>33.0</v>
       </c>
-      <c r="H124" s="16">
+      <c r="H124" s="17">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
@@ -8962,7 +8969,7 @@
       <c r="D125" s="4">
         <v>33.0</v>
       </c>
-      <c r="H125" s="16">
+      <c r="H125" s="17">
         <f t="shared" si="3"/>
         <v>27</v>
       </c>
@@ -8980,7 +8987,7 @@
       <c r="D126" s="4">
         <v>33.0</v>
       </c>
-      <c r="H126" s="16">
+      <c r="H126" s="17">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
@@ -8998,7 +9005,7 @@
       <c r="D127" s="4">
         <v>33.0</v>
       </c>
-      <c r="H127" s="16">
+      <c r="H127" s="17">
         <f t="shared" si="3"/>
         <v>29</v>
       </c>
@@ -9016,7 +9023,7 @@
       <c r="D128" s="4">
         <v>33.0</v>
       </c>
-      <c r="H128" s="16">
+      <c r="H128" s="17">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
@@ -9034,7 +9041,7 @@
       <c r="D129" s="4">
         <v>33.0</v>
       </c>
-      <c r="H129" s="16">
+      <c r="H129" s="17">
         <f t="shared" si="3"/>
         <v>31</v>
       </c>
@@ -9052,7 +9059,7 @@
       <c r="D130" s="4">
         <v>33.0</v>
       </c>
-      <c r="H130" s="16">
+      <c r="H130" s="17">
         <f t="shared" si="3"/>
         <v>32</v>
       </c>
@@ -9070,7 +9077,7 @@
       <c r="D131" s="4">
         <v>33.0</v>
       </c>
-      <c r="H131" s="16">
+      <c r="H131" s="17">
         <f t="shared" si="3"/>
         <v>33</v>
       </c>
@@ -9088,7 +9095,7 @@
       <c r="D132" s="4">
         <v>33.0</v>
       </c>
-      <c r="H132" s="16">
+      <c r="H132" s="17">
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
@@ -9106,7 +9113,7 @@
       <c r="D133" s="4">
         <v>33.0</v>
       </c>
-      <c r="H133" s="16">
+      <c r="H133" s="17">
         <f t="shared" si="3"/>
         <v>35</v>
       </c>
@@ -9124,7 +9131,7 @@
       <c r="D134" s="4">
         <v>33.0</v>
       </c>
-      <c r="H134" s="16">
+      <c r="H134" s="17">
         <f t="shared" si="3"/>
         <v>36</v>
       </c>
@@ -9142,7 +9149,7 @@
       <c r="D135" s="4">
         <v>33.0</v>
       </c>
-      <c r="H135" s="16">
+      <c r="H135" s="17">
         <f t="shared" si="3"/>
         <v>37</v>
       </c>
@@ -9160,7 +9167,7 @@
       <c r="D136" s="4">
         <v>33.0</v>
       </c>
-      <c r="H136" s="16">
+      <c r="H136" s="17">
         <f t="shared" si="3"/>
         <v>38</v>
       </c>
@@ -9178,10 +9185,10 @@
       <c r="D137" s="4">
         <v>33.0</v>
       </c>
-      <c r="I137" s="13">
+      <c r="I137" s="14">
         <v>1.0</v>
       </c>
-      <c r="K137" s="13"/>
+      <c r="K137" s="14"/>
     </row>
     <row r="138" ht="22.5" customHeight="1">
       <c r="A138" s="6" t="s">
@@ -9196,7 +9203,7 @@
       <c r="D138" s="4">
         <v>33.0</v>
       </c>
-      <c r="I138" s="16">
+      <c r="I138" s="17">
         <f t="shared" ref="I138:I160" si="4">I137+1</f>
         <v>2</v>
       </c>
@@ -9214,7 +9221,7 @@
       <c r="D139" s="4">
         <v>33.0</v>
       </c>
-      <c r="I139" s="16">
+      <c r="I139" s="17">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
@@ -9232,7 +9239,7 @@
       <c r="D140" s="4">
         <v>33.0</v>
       </c>
-      <c r="I140" s="16">
+      <c r="I140" s="17">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
@@ -9250,7 +9257,7 @@
       <c r="D141" s="4">
         <v>33.0</v>
       </c>
-      <c r="I141" s="16">
+      <c r="I141" s="17">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
@@ -9268,7 +9275,7 @@
       <c r="D142" s="4">
         <v>33.0</v>
       </c>
-      <c r="I142" s="16">
+      <c r="I142" s="17">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
@@ -9286,7 +9293,7 @@
       <c r="D143" s="4">
         <v>33.0</v>
       </c>
-      <c r="I143" s="16">
+      <c r="I143" s="17">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
@@ -9304,7 +9311,7 @@
       <c r="D144" s="4">
         <v>33.0</v>
       </c>
-      <c r="I144" s="16">
+      <c r="I144" s="17">
         <f t="shared" si="4"/>
         <v>8</v>
       </c>
@@ -9322,7 +9329,7 @@
       <c r="D145" s="4">
         <v>33.0</v>
       </c>
-      <c r="I145" s="16">
+      <c r="I145" s="17">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
@@ -9340,7 +9347,7 @@
       <c r="D146" s="4">
         <v>33.0</v>
       </c>
-      <c r="I146" s="16">
+      <c r="I146" s="17">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
@@ -9358,7 +9365,7 @@
       <c r="D147" s="4">
         <v>33.0</v>
       </c>
-      <c r="I147" s="16">
+      <c r="I147" s="17">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
@@ -9376,7 +9383,7 @@
       <c r="D148" s="4">
         <v>33.0</v>
       </c>
-      <c r="I148" s="16">
+      <c r="I148" s="17">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
@@ -9394,7 +9401,7 @@
       <c r="D149" s="4">
         <v>33.0</v>
       </c>
-      <c r="I149" s="16">
+      <c r="I149" s="17">
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
@@ -9412,7 +9419,7 @@
       <c r="D150" s="4">
         <v>33.0</v>
       </c>
-      <c r="I150" s="16">
+      <c r="I150" s="17">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
@@ -9430,7 +9437,7 @@
       <c r="D151" s="4">
         <v>33.0</v>
       </c>
-      <c r="I151" s="16">
+      <c r="I151" s="17">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
@@ -9448,7 +9455,7 @@
       <c r="D152" s="4">
         <v>33.0</v>
       </c>
-      <c r="I152" s="16">
+      <c r="I152" s="17">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
@@ -9466,7 +9473,7 @@
       <c r="D153" s="4">
         <v>33.0</v>
       </c>
-      <c r="I153" s="16">
+      <c r="I153" s="17">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
@@ -9484,7 +9491,7 @@
       <c r="D154" s="4">
         <v>33.0</v>
       </c>
-      <c r="I154" s="16">
+      <c r="I154" s="17">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
@@ -9502,7 +9509,7 @@
       <c r="D155" s="4">
         <v>33.0</v>
       </c>
-      <c r="I155" s="16">
+      <c r="I155" s="17">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
@@ -9520,7 +9527,7 @@
       <c r="D156" s="4">
         <v>33.0</v>
       </c>
-      <c r="I156" s="16">
+      <c r="I156" s="17">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
@@ -9538,7 +9545,7 @@
       <c r="D157" s="4">
         <v>33.0</v>
       </c>
-      <c r="I157" s="16">
+      <c r="I157" s="17">
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
@@ -9556,7 +9563,7 @@
       <c r="D158" s="4">
         <v>33.0</v>
       </c>
-      <c r="I158" s="16">
+      <c r="I158" s="17">
         <f t="shared" si="4"/>
         <v>22</v>
       </c>
@@ -9574,7 +9581,7 @@
       <c r="D159" s="4">
         <v>33.0</v>
       </c>
-      <c r="I159" s="16">
+      <c r="I159" s="17">
         <f t="shared" si="4"/>
         <v>23</v>
       </c>
@@ -9592,7 +9599,7 @@
       <c r="D160" s="4">
         <v>33.0</v>
       </c>
-      <c r="I160" s="16">
+      <c r="I160" s="17">
         <f t="shared" si="4"/>
         <v>24</v>
       </c>
@@ -9607,7 +9614,7 @@
       <c r="C161" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="D161" s="19">
+      <c r="D161" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -9621,7 +9628,7 @@
       <c r="C162" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="D162" s="19">
+      <c r="D162" s="20">
         <v>25.0</v>
       </c>
     </row>
@@ -9666,10 +9673,10 @@
       <c r="D165" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="G165" s="13"/>
-      <c r="H165" s="13"/>
-      <c r="I165" s="13"/>
-      <c r="J165" s="13">
+      <c r="G165" s="14"/>
+      <c r="H165" s="14"/>
+      <c r="I165" s="14"/>
+      <c r="J165" s="14">
         <v>1.0</v>
       </c>
     </row>
@@ -9686,7 +9693,7 @@
       <c r="D166" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J166" s="16">
+      <c r="J166" s="17">
         <f t="shared" ref="J166:J192" si="5">J165+1</f>
         <v>2</v>
       </c>
@@ -9704,7 +9711,7 @@
       <c r="D167" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J167" s="16">
+      <c r="J167" s="17">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -9722,7 +9729,7 @@
       <c r="D168" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J168" s="16">
+      <c r="J168" s="17">
         <f t="shared" si="5"/>
         <v>4</v>
       </c>
@@ -9740,7 +9747,7 @@
       <c r="D169" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J169" s="16">
+      <c r="J169" s="17">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
@@ -9758,7 +9765,7 @@
       <c r="D170" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J170" s="16">
+      <c r="J170" s="17">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
@@ -9776,7 +9783,7 @@
       <c r="D171" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J171" s="16">
+      <c r="J171" s="17">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
@@ -9794,7 +9801,7 @@
       <c r="D172" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J172" s="16">
+      <c r="J172" s="17">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
@@ -9812,7 +9819,7 @@
       <c r="D173" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J173" s="16">
+      <c r="J173" s="17">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
@@ -9830,7 +9837,7 @@
       <c r="D174" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J174" s="16">
+      <c r="J174" s="17">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
@@ -9848,7 +9855,7 @@
       <c r="D175" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J175" s="16">
+      <c r="J175" s="17">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
@@ -9866,7 +9873,7 @@
       <c r="D176" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J176" s="16">
+      <c r="J176" s="17">
         <f t="shared" si="5"/>
         <v>12</v>
       </c>
@@ -9884,7 +9891,7 @@
       <c r="D177" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J177" s="16">
+      <c r="J177" s="17">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
@@ -9902,7 +9909,7 @@
       <c r="D178" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J178" s="16">
+      <c r="J178" s="17">
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
@@ -9920,7 +9927,7 @@
       <c r="D179" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J179" s="16">
+      <c r="J179" s="17">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
@@ -9938,7 +9945,7 @@
       <c r="D180" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J180" s="16">
+      <c r="J180" s="17">
         <f t="shared" si="5"/>
         <v>16</v>
       </c>
@@ -9956,7 +9963,7 @@
       <c r="D181" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J181" s="16">
+      <c r="J181" s="17">
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
@@ -9974,7 +9981,7 @@
       <c r="D182" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J182" s="16">
+      <c r="J182" s="17">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
@@ -9992,7 +9999,7 @@
       <c r="D183" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J183" s="16">
+      <c r="J183" s="17">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
@@ -10010,7 +10017,7 @@
       <c r="D184" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J184" s="16">
+      <c r="J184" s="17">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
@@ -10028,7 +10035,7 @@
       <c r="D185" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J185" s="16">
+      <c r="J185" s="17">
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
@@ -10046,7 +10053,7 @@
       <c r="D186" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J186" s="16">
+      <c r="J186" s="17">
         <f t="shared" si="5"/>
         <v>22</v>
       </c>
@@ -10064,7 +10071,7 @@
       <c r="D187" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J187" s="16">
+      <c r="J187" s="17">
         <f t="shared" si="5"/>
         <v>23</v>
       </c>
@@ -10082,7 +10089,7 @@
       <c r="D188" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J188" s="16">
+      <c r="J188" s="17">
         <f t="shared" si="5"/>
         <v>24</v>
       </c>
@@ -10100,7 +10107,7 @@
       <c r="D189" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J189" s="16">
+      <c r="J189" s="17">
         <f t="shared" si="5"/>
         <v>25</v>
       </c>
@@ -10118,7 +10125,7 @@
       <c r="D190" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J190" s="16">
+      <c r="J190" s="17">
         <f t="shared" si="5"/>
         <v>26</v>
       </c>
@@ -10136,7 +10143,7 @@
       <c r="D191" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J191" s="16">
+      <c r="J191" s="17">
         <f t="shared" si="5"/>
         <v>27</v>
       </c>
@@ -10154,7 +10161,7 @@
       <c r="D192" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="J192" s="16">
+      <c r="J192" s="17">
         <f t="shared" si="5"/>
         <v>28</v>
       </c>
@@ -10172,11 +10179,11 @@
       <c r="D193" s="4">
         <v>33.0</v>
       </c>
-      <c r="G193" s="13"/>
-      <c r="H193" s="13"/>
-      <c r="I193" s="13"/>
-      <c r="J193" s="13"/>
-      <c r="K193" s="13">
+      <c r="G193" s="14"/>
+      <c r="H193" s="14"/>
+      <c r="I193" s="14"/>
+      <c r="J193" s="14"/>
+      <c r="K193" s="14">
         <v>1.0</v>
       </c>
     </row>
@@ -10193,7 +10200,7 @@
       <c r="D194" s="4">
         <v>33.0</v>
       </c>
-      <c r="K194" s="16">
+      <c r="K194" s="17">
         <f t="shared" ref="K194:K214" si="6">K193+1</f>
         <v>2</v>
       </c>
@@ -10211,7 +10218,7 @@
       <c r="D195" s="4">
         <v>33.0</v>
       </c>
-      <c r="K195" s="16">
+      <c r="K195" s="17">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
@@ -10229,7 +10236,7 @@
       <c r="D196" s="4">
         <v>33.0</v>
       </c>
-      <c r="K196" s="16">
+      <c r="K196" s="17">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
@@ -10247,7 +10254,7 @@
       <c r="D197" s="4">
         <v>33.0</v>
       </c>
-      <c r="K197" s="16">
+      <c r="K197" s="17">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
@@ -10265,7 +10272,7 @@
       <c r="D198" s="4">
         <v>33.0</v>
       </c>
-      <c r="K198" s="16">
+      <c r="K198" s="17">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
@@ -10283,7 +10290,7 @@
       <c r="D199" s="4">
         <v>33.0</v>
       </c>
-      <c r="K199" s="16">
+      <c r="K199" s="17">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
@@ -10301,7 +10308,7 @@
       <c r="D200" s="4">
         <v>33.0</v>
       </c>
-      <c r="K200" s="16">
+      <c r="K200" s="17">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
@@ -10319,7 +10326,7 @@
       <c r="D201" s="4">
         <v>33.0</v>
       </c>
-      <c r="K201" s="16">
+      <c r="K201" s="17">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
@@ -10337,7 +10344,7 @@
       <c r="D202" s="4">
         <v>33.0</v>
       </c>
-      <c r="K202" s="16">
+      <c r="K202" s="17">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
@@ -10355,7 +10362,7 @@
       <c r="D203" s="4">
         <v>33.0</v>
       </c>
-      <c r="K203" s="16">
+      <c r="K203" s="17">
         <f t="shared" si="6"/>
         <v>11</v>
       </c>
@@ -10373,7 +10380,7 @@
       <c r="D204" s="4">
         <v>33.0</v>
       </c>
-      <c r="K204" s="16">
+      <c r="K204" s="17">
         <f t="shared" si="6"/>
         <v>12</v>
       </c>
@@ -10391,7 +10398,7 @@
       <c r="D205" s="4">
         <v>33.0</v>
       </c>
-      <c r="K205" s="16">
+      <c r="K205" s="17">
         <f t="shared" si="6"/>
         <v>13</v>
       </c>
@@ -10409,7 +10416,7 @@
       <c r="D206" s="4">
         <v>33.0</v>
       </c>
-      <c r="K206" s="16">
+      <c r="K206" s="17">
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
@@ -10427,7 +10434,7 @@
       <c r="D207" s="4">
         <v>33.0</v>
       </c>
-      <c r="K207" s="16">
+      <c r="K207" s="17">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
@@ -10445,7 +10452,7 @@
       <c r="D208" s="4">
         <v>33.0</v>
       </c>
-      <c r="K208" s="16">
+      <c r="K208" s="17">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
@@ -10463,7 +10470,7 @@
       <c r="D209" s="4">
         <v>33.0</v>
       </c>
-      <c r="K209" s="16">
+      <c r="K209" s="17">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
@@ -10481,7 +10488,7 @@
       <c r="D210" s="4">
         <v>33.0</v>
       </c>
-      <c r="K210" s="16">
+      <c r="K210" s="17">
         <f t="shared" si="6"/>
         <v>18</v>
       </c>
@@ -10499,7 +10506,7 @@
       <c r="D211" s="4">
         <v>33.0</v>
       </c>
-      <c r="K211" s="16">
+      <c r="K211" s="17">
         <f t="shared" si="6"/>
         <v>19</v>
       </c>
@@ -10517,7 +10524,7 @@
       <c r="D212" s="4">
         <v>33.0</v>
       </c>
-      <c r="K212" s="16">
+      <c r="K212" s="17">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
@@ -10535,7 +10542,7 @@
       <c r="D213" s="4">
         <v>33.0</v>
       </c>
-      <c r="K213" s="16">
+      <c r="K213" s="17">
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
@@ -10553,7 +10560,7 @@
       <c r="D214" s="4">
         <v>33.0</v>
       </c>
-      <c r="K214" s="16">
+      <c r="K214" s="17">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
@@ -10585,30 +10592,30 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="2">
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>685</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>686</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>687</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="14" t="s">
         <v>688</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="22" t="s">
         <v>689</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="14" t="s">
         <v>690</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="22" t="s">
         <v>691</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="H4" s="14" t="s">
         <v>692</v>
       </c>
     </row>
@@ -10628,66 +10635,66 @@
   </cols>
   <sheetData>
     <row r="7">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="14" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="14" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14" t="s">
         <v>239</v>
       </c>
     </row>
